--- a/output/sliding_window_results_window_12.xlsx
+++ b/output/sliding_window_results_window_12.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>38.09307665037371</v>
+        <v>66.10876777573429</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4069233496262896</v>
+        <v>6.108767775734293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1655866124710795</v>
+        <v>37.3170437378497</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C3" t="n">
-        <v>39.68951104039833</v>
+        <v>73.02208172497083</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4104889596016719</v>
+        <v>9.122081724970833</v>
       </c>
       <c r="E3" t="n">
-        <v>0.168501185954863</v>
+        <v>83.21237499704685</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>40.87684232238721</v>
+        <v>77.40450130016482</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6231576776127881</v>
+        <v>6.80450130016483</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3883254911677635</v>
+        <v>46.30123794394486</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>43.95739158816144</v>
+        <v>86.3898243929727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2573915881614397</v>
+        <v>5.489824392972693</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06625042965626819</v>
+        <v>30.138171865678</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>46.78306782113736</v>
+        <v>92.84293650615909</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.316932178862643</v>
+        <v>3.742936506159097</v>
       </c>
       <c r="E6" t="n">
-        <v>1.734310363723909</v>
+        <v>14.00957368913847</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>51.8429606362786</v>
+        <v>87.94211132207536</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.157039363721395</v>
+        <v>-7.057888677924637</v>
       </c>
       <c r="E7" t="n">
-        <v>1.338740089200811</v>
+        <v>49.81379258997679</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C8" t="n">
-        <v>55.4269665107689</v>
+        <v>100.5954604547057</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6730334892311021</v>
+        <v>1.795460454705719</v>
       </c>
       <c r="E8" t="n">
-        <v>0.452974077626592</v>
+        <v>3.223678244412066</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C9" t="n">
-        <v>58.93933341239186</v>
+        <v>100.2349501888288</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.060666587608139</v>
+        <v>-3.065049811171235</v>
       </c>
       <c r="E9" t="n">
-        <v>1.125013610068295</v>
+        <v>9.394530344960824</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>62.6231163368272</v>
+        <v>108.1787885585579</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.276883663172804</v>
+        <v>1.178788558557855</v>
       </c>
       <c r="E10" t="n">
-        <v>1.630431889277598</v>
+        <v>1.389542465786906</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C11" t="n">
-        <v>70.13951622966773</v>
+        <v>117.981116101864</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4604837703322602</v>
+        <v>9.281116101864015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2120453027394137</v>
+        <v>86.13911609627949</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C12" t="n">
-        <v>78.76192453394441</v>
+        <v>118.7927966204576</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.138075466055597</v>
+        <v>6.092796620457577</v>
       </c>
       <c r="E12" t="n">
-        <v>4.571366698548856</v>
+        <v>37.12217065825927</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C13" t="n">
-        <v>86.98369765902464</v>
+        <v>127.5435400404217</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.116302340975352</v>
+        <v>10.34354004042173</v>
       </c>
       <c r="E13" t="n">
-        <v>4.478735598417756</v>
+        <v>106.9888205678076</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C14" t="n">
-        <v>92.84591188735541</v>
+        <v>126.4025657097683</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.154088112644587</v>
+        <v>3.302565709768288</v>
       </c>
       <c r="E14" t="n">
-        <v>4.640095597036718</v>
+        <v>10.90694026733732</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C15" t="n">
-        <v>97.0993879756053</v>
+        <v>130.8840162148707</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.700612024394701</v>
+        <v>1.98401621487065</v>
       </c>
       <c r="E15" t="n">
-        <v>2.892081257515843</v>
+        <v>3.93632034086966</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>103.3</v>
+        <v>135.1</v>
       </c>
       <c r="C16" t="n">
-        <v>100.9646620393917</v>
+        <v>141.1789020399588</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.335337960608314</v>
+        <v>6.078902039958763</v>
       </c>
       <c r="E16" t="n">
-        <v>5.453803390258198</v>
+        <v>36.95305001141481</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>107</v>
+        <v>139.4</v>
       </c>
       <c r="C17" t="n">
-        <v>105.1367852342856</v>
+        <v>145.5271477168797</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.863214765714432</v>
+        <v>6.127147716879648</v>
       </c>
       <c r="E17" t="n">
-        <v>3.471569263176284</v>
+        <v>37.54193914446348</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>108.7</v>
+        <v>143.8</v>
       </c>
       <c r="C18" t="n">
-        <v>107.2921409644417</v>
+        <v>146.9129372607229</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.407859035558289</v>
+        <v>3.112937260722845</v>
       </c>
       <c r="E18" t="n">
-        <v>1.982067064003115</v>
+        <v>9.690378389196647</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>112.7</v>
+        <v>147.2</v>
       </c>
       <c r="C19" t="n">
-        <v>111.9709610074357</v>
+        <v>154.3395455739006</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7290389925642558</v>
+        <v>7.139545573900591</v>
       </c>
       <c r="E19" t="n">
-        <v>0.531497852679105</v>
+        <v>50.97311100180352</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>117.2</v>
+        <v>151.8</v>
       </c>
       <c r="C20" t="n">
-        <v>114.9510710589404</v>
+        <v>158.131574923761</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.248928941059589</v>
+        <v>6.331574923760968</v>
       </c>
       <c r="E20" t="n">
-        <v>5.057681381935403</v>
+        <v>40.08884101519871</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>123.1</v>
+        <v>156.1</v>
       </c>
       <c r="C21" t="n">
-        <v>122.3556494254586</v>
+        <v>162.1337323740562</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7443505745413574</v>
+        <v>6.033732374056171</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5540577778200489</v>
+        <v>36.40592636173352</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-24.56602566572413</v>
+        <v>89.94729680083069</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>40.91513493327792</v>
+        <v>731.5465597331586</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>2.045756746663896</v>
+        <v>36.57732798665793</v>
       </c>
     </row>
   </sheetData>
